--- a/Progress/Company wise/google/google_prep_questions.xlsx
+++ b/Progress/Company wise/google/google_prep_questions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Topics</t>
         </is>
       </c>
     </row>
@@ -2955,6 +2955,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1.11 String - Advanced</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>Longest Duplicate Substring</t>
@@ -2973,8 +2978,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>String / Binary Search / Rolling Hash</t>
+        </is>
+      </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1.11 String - Advanced</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>Longest Happy Prefix</t>
@@ -2993,8 +3008,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>String / KMP / Z-algorithm</t>
+        </is>
+      </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1.11 String - Advanced</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>Shortest Palindrome</t>
@@ -3013,8 +3038,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>String / KMP / Rolling Hash</t>
+        </is>
+      </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1.12 Game Theory</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
           <t>Stone Game II</t>
@@ -3033,8 +3068,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Math / Game Theory / DP</t>
+        </is>
+      </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1.12 Game Theory</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>Stone Game</t>
@@ -3053,8 +3098,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Math / Game Theory / DP</t>
+        </is>
+      </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1.13 Interactive Problems</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>Guess the Word</t>
@@ -3073,8 +3128,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Array / String / Interactive</t>
+        </is>
+      </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1.8 DP - Advanced</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>House Robber III</t>
@@ -3093,8 +3158,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tree / DFS / DP</t>
+        </is>
+      </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1.8 DP - Advanced</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>Strange Printer</t>
@@ -3113,8 +3188,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>String / DP / Interval DP</t>
+        </is>
+      </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1.10 Greedy</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
           <t>IPO</t>
@@ -3133,8 +3218,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Array / Greedy / Heap</t>
+        </is>
+      </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1.8 DP - Advanced</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>Minimum Cost to Hire K Workers</t>
@@ -3153,8 +3248,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Array / Greedy / Heap / Sorting</t>
+        </is>
+      </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1.10 Greedy</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>Minimum Number of Refueling Stops</t>
@@ -3173,8 +3278,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Array / Greedy / Heap</t>
+        </is>
+      </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1.10 Greedy</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>Candy</t>
@@ -3193,8 +3308,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Array / Greedy</t>
+        </is>
+      </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1.9 Maths</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>Super Pow</t>
@@ -3213,8 +3338,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Math / Divide and Conquer</t>
+        </is>
+      </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1.9 Maths</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>Count Primes</t>
@@ -3233,8 +3368,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Array / Math / Number Theory</t>
+        </is>
+      </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1.5 Prefix Sum / Difference Array</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>Car Pooling</t>
@@ -3253,8 +3398,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Array / Sorting / Prefix Sum</t>
+        </is>
+      </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1.7 Geometry / Line Sweep</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>Meeting Rooms II</t>
@@ -3273,8 +3428,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Array / Two Pointers / Sorting / Heap</t>
+        </is>
+      </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1.14 Advanced Graph</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>Minimum Number of Days to Disconnect Island</t>
@@ -3293,8 +3458,18 @@
           <t>Done</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Array / DFS / BFS / Articulation Point</t>
+        </is>
+      </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1.14 Advanced Graph</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
           <t>Sum of Distances in Tree</t>
@@ -3311,6 +3486,41 @@
       <c r="F87" t="inlineStr">
         <is>
           <t>Done</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tree / DFS / Graph / Rerooting</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1.8 DP - Advanced</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Numbers At Most N Given Digit Set</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>902</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>digit dp</t>
         </is>
       </c>
     </row>

--- a/Progress/Company wise/google/google_prep_questions.xlsx
+++ b/Progress/Company wise/google/google_prep_questions.xlsx
@@ -1,32 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Google Prep Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Google Prep Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,14 +41,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -203,6 +194,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -237,6 +229,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -271,20 +264,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -406,7 +395,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -417,50 +445,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>LC#</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Topics</t>
         </is>
@@ -642,7 +661,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1049,7 +1068,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1234,7 +1253,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Not Done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2729,16 +2748,20 @@
           <t>1.8 DP - Advanced</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>62</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>Painting a Grid With Three Different Colors</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>1931</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2762,16 +2785,20 @@
           <t>1.9 Maths</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>63</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>Unique Paths</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>62</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2795,16 +2822,20 @@
           <t>1.9 Maths</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>64</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>Fibonacci Number (Matrix Expo)</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>509</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2828,16 +2859,20 @@
           <t>1.14 Advanced Graph</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>65</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
           <t>Reconstruct Itinerary</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>332</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2861,16 +2896,20 @@
           <t>1.18 Divide &amp; Conquer - Advanced</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>66</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>Kth Largest Element in an Array</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>215</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2894,16 +2933,20 @@
           <t>1.20 Randomized Algorithms</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>67</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>Kth Largest Element in an Array</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>215</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2927,16 +2970,20 @@
           <t>1.20 Randomized Algorithms</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>68</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
           <t>Shuffle an Array</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>384</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2965,8 +3012,10 @@
           <t>Longest Duplicate Substring</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>1044</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2995,8 +3044,10 @@
           <t>Longest Happy Prefix</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>1392</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3025,8 +3076,10 @@
           <t>Shortest Palindrome</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>214</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3055,8 +3108,10 @@
           <t>Stone Game II</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>1140</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3085,8 +3140,10 @@
           <t>Stone Game</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>877</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3115,8 +3172,10 @@
           <t>Guess the Word</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>843</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3145,8 +3204,10 @@
           <t>House Robber III</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>337</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3175,8 +3236,10 @@
           <t>Strange Printer</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>664</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,8 +3268,10 @@
           <t>IPO</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>502</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3235,8 +3300,10 @@
           <t>Minimum Cost to Hire K Workers</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>857</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3265,8 +3332,10 @@
           <t>Minimum Number of Refueling Stops</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>871</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3295,8 +3364,10 @@
           <t>Candy</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>135</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3325,8 +3396,10 @@
           <t>Super Pow</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>372</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3355,8 +3428,10 @@
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>204</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3385,8 +3460,10 @@
           <t>Car Pooling</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>1094</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3415,8 +3492,10 @@
           <t>Meeting Rooms II</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>253</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3445,8 +3524,10 @@
           <t>Minimum Number of Days to Disconnect Island</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>1568</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3475,8 +3556,10 @@
           <t>Sum of Distances in Tree</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>834</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3505,8 +3588,10 @@
           <t>Numbers At Most N Given Digit Set</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>902</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3521,6 +3606,132 @@
       <c r="G88" t="inlineStr">
         <is>
           <t>digit dp</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1.8 DP - Advanced</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Count of Integers</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>digit dp</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1.5 Prefix Sum / Difference Array</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Maximum Sum Obtained of Any Permutation</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1589</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Diff Array / Greedy</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1.8 DP - Advanced</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Maximum Building Height</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Greedy / Two Pass / Simplified CHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1.8 DP - Advanced</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Count Array Pairs Divisible by K</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2183</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Array / Math / Number Theory / GCD</t>
         </is>
       </c>
     </row>

--- a/Progress/Company wise/google/google_prep_questions.xlsx
+++ b/Progress/Company wise/google/google_prep_questions.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3706,7 +3706,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1.8 DP - Advanced</t>
+          <t>1.9 Maths</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3732,6 +3732,134 @@
       <c r="G92" t="inlineStr">
         <is>
           <t>Array / Math / Number Theory / GCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1.9 Maths</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Count All Valid Pickup and Delivery Options</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Math / Combinatorics / AP Series</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1.11 String - Advanced</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Repeated DNA Sequences</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>String / Rolling Hash / Rabin-Karp</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1.10 Greedy</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Stamping the Sequence</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>String / Greedy / Reverse Simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1.11 String - Advanced</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Maximum Number of Non-Overlapping Palindrome Substrings</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>String / Palindrome DP / Interval DP</t>
         </is>
       </c>
     </row>

--- a/Progress/Company wise/google/google_prep_questions.xlsx
+++ b/Progress/Company wise/google/google_prep_questions.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,6 +3863,70 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1.12 Game Theory</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Stone Game IV</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Game Theory / Sprague-Grundy / DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1.12 Game Theory</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Can I Win</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Game Theory / Bitmask DP / Memoized Search</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
